--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA165"/>
+  <dimension ref="A1:AA166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17244,6 +17244,111 @@
       <c r="Z165" s="2" t="inlineStr"/>
       <c r="AA165" s="2" t="inlineStr"/>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>La Nacional De Licores De Colombia Sas</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>La Nacional De Licores De Colombia Sas</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>114212</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>12-36 Carrera 18, Estanzuela</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>111411</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://lanacionaldelicores.com</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>nacho@lanacionaldelicores.com</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>9003780885</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-nacional-de-licores</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LaNacionalDeLicores/</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lanacionaldelicores</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>Nelson Pablo Cruz Cabrera</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nelson-pablo-cruz-cabrera-a1b9a2123/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA166"/>
+  <dimension ref="A1:AA169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17349,6 +17349,289 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>21983</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>1050 Calle 81, El Nogal</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>ventascorporativas@thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr"/>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr"/>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-wine-store/</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr"/>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thewinestoreco</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>Luis Fernando</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-fernando-luque-6625729/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>21983</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>1050 Calle 81, El Nogal</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>ventascorporativas@thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr"/>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr"/>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-wine-store/</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr"/>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thewinestoreco</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>Andrea Cuellar</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Spirits Manager</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrea-cuellar-aa349471/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>La Nacional De Licores De Colombia Sas</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>La Nacional De Licores De Colombia Sas</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>114212</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>12-36 Carrera 18, Estanzuela</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>111411</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://lanacionaldelicores.com</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>nacho@lanacionaldelicores.com</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr"/>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>9003780885</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-nacional-de-licores</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LaNacionalDeLicores/</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lanacionaldelicores</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>Nelson Pablo Cruz Cabrera</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nelson-pablo-cruz-cabrera-a1b9a2123/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA169"/>
+  <dimension ref="A1:AA172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17632,6 +17632,289 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>21983</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>1050 Calle 81, El Nogal</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>ventascorporativas@thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr"/>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr"/>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-wine-store/</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr"/>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thewinestoreco</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>Luis Fernando</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-fernando-luque-6625729/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>21983</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>1050 Calle 81, El Nogal</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>ventascorporativas@thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr"/>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr"/>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-wine-store/</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thewinestoreco</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>Andrea Cuellar</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Spirits Manager</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrea-cuellar-aa349471/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>La Nacional De Licores De Colombia Sas</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>La Nacional De Licores De Colombia Sas</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>114212</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>12-36 Carrera 18, Estanzuela</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>111411</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://lanacionaldelicores.com</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>nacho@lanacionaldelicores.com</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr"/>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>9003780885</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-nacional-de-licores</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LaNacionalDeLicores/</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lanacionaldelicores</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>Nelson Pablo Cruz Cabrera</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nelson-pablo-cruz-cabrera-a1b9a2123/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA172"/>
+  <dimension ref="A1:AA176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17915,6 +17915,390 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Madero S A S</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Grupo Madero S A S</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>108908</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>85a-75 Carrera 22a, Polo Club</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>111211</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://badranmarket.co</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>info@grupomadero.com.co</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr"/>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>9004766164</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/badran.buenavida/</t>
+        </is>
+      </c>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC9XNOR_Pqk4cHbNIsWGfgBQ</t>
+        </is>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>Fadia Badrán</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fadia-badr%C3%A1n-50173046/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>21983</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>1050 Calle 81, El Nogal</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>ventascorporativas@thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr"/>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr"/>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-wine-store/</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr"/>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thewinestoreco</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>Luis Fernando</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-fernando-luque-6625729/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Store</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>21983</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>1050 Calle 81, El Nogal</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>ventascorporativas@thewinestore.com.co</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr"/>
+      <c r="P175" s="2" t="inlineStr"/>
+      <c r="Q175" s="2" t="inlineStr"/>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-wine-store/</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr"/>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thewinestoreco</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>Andrea Cuellar</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>Wine &amp; Spirits Manager</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrea-cuellar-aa349471/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>La Nacional De Licores De Colombia Sas</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>La Nacional De Licores De Colombia Sas</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>114212</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>12-36 Carrera 18, Estanzuela</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>111411</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://lanacionaldelicores.com</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>nacho@lanacionaldelicores.com</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr"/>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>9003780885</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-nacional-de-licores</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LaNacionalDeLicores/</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lanacionaldelicores</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>Nelson Pablo Cruz Cabrera</t>
+        </is>
+      </c>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nelson-pablo-cruz-cabrera-a1b9a2123/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
